--- a/sims/temporal_lp_economics_MODEL_v5_options_seller.xlsx
+++ b/sims/temporal_lp_economics_MODEL_v5_options_seller.xlsx
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="B13" s="15">
-        <f>B8+B9+B10+B11</f>
+        <f>B9+B10+B11+B12</f>
         <v/>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="B15" s="15">
-        <f>B12+B13</f>
+        <f>B13+B14</f>
         <v/>
       </c>
     </row>
